--- a/Data_analytics/LabWeek2.xlsx
+++ b/Data_analytics/LabWeek2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bambook/offTop/Data_analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7C908D-0B65-FA45-B173-48195D3BC9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C294B40-F9D8-2B4B-BA85-1472B95D6C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19660" yWindow="12180" windowWidth="27460" windowHeight="16160" activeTab="3" xr2:uid="{550FC0EE-6C08-C446-B890-EA0D6560BA48}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{550FC0EE-6C08-C446-B890-EA0D6560BA48}"/>
   </bookViews>
   <sheets>
     <sheet name="Cleaning (removed dbl)" sheetId="5" r:id="rId1"/>
@@ -23,17 +23,25 @@
     <sheet name="Products" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="Slicer_cleanCountry">#N/A</definedName>
+    <definedName name="Slicer_cleanProfuct">#N/A</definedName>
+    <definedName name="Slicer_Month">#N/A</definedName>
     <definedName name="Slicer_Region">#N/A</definedName>
+    <definedName name="Slicer_Revenue">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId9"/>
-    <pivotCache cacheId="16" r:id="rId10"/>
+    <pivotCache cacheId="22" r:id="rId9"/>
+    <pivotCache cacheId="23" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId11"/>
+        <x14:slicerCache r:id="rId12"/>
+        <x14:slicerCache r:id="rId13"/>
+        <x14:slicerCache r:id="rId14"/>
+        <x14:slicerCache r:id="rId15"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -58,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="87">
   <si>
     <t>Region</t>
   </si>
@@ -284,6 +292,42 @@
   <si>
     <t>Sum of Revenue</t>
   </si>
+  <si>
+    <t>electronic</t>
+  </si>
+  <si>
+    <t>furniture</t>
+  </si>
+  <si>
+    <t>iohone10</t>
+  </si>
+  <si>
+    <t>iohone11</t>
+  </si>
+  <si>
+    <t>chair</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>ipad1</t>
+  </si>
+  <si>
+    <t>sofa</t>
+  </si>
+  <si>
+    <t>bed</t>
+  </si>
+  <si>
+    <t>iphone7</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>Count of  Sales</t>
+  </si>
 </sst>
 </file>
 
@@ -352,14 +396,164 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -427,7 +621,9 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent1">
+              <a:alpha val="70000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -435,7 +631,19 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -468,8 +676,9 @@
               <a:endParaRPr lang="en-KG"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -483,7 +692,9 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent1">
+              <a:alpha val="70000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -491,7 +702,19 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -524,8 +747,9 @@
               <a:endParaRPr lang="en-KG"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -539,7 +763,9 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent1">
+              <a:alpha val="70000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -547,7 +773,19 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -580,8 +818,9 @@
               <a:endParaRPr lang="en-KG"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -595,7 +834,9 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent1">
+              <a:alpha val="70000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -603,7 +844,19 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -636,8 +889,9 @@
               <a:endParaRPr lang="en-KG"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -680,7 +934,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent1">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -688,6 +944,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-KG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>PivotDemo!$H$5:$H$9</c:f>
@@ -751,7 +1064,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent2">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -759,6 +1074,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-KG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>PivotDemo!$H$5:$H$9</c:f>
@@ -802,7 +1174,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F98D-ED40-B732-972F357C477B}"/>
+              <c16:uniqueId val="{00000002-6E7A-6A4E-A238-64DAA2D793D4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -822,7 +1194,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent3">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -830,6 +1204,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-KG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>PivotDemo!$H$5:$H$9</c:f>
@@ -873,7 +1304,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-F98D-ED40-B732-972F357C477B}"/>
+              <c16:uniqueId val="{00000003-6E7A-6A4E-A238-64DAA2D793D4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -893,7 +1324,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4"/>
+              <a:schemeClr val="accent4">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -901,6 +1334,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-KG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>PivotDemo!$H$5:$H$9</c:f>
@@ -935,20 +1425,21 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-F98D-ED40-B732-972F357C477B}"/>
+              <c16:uniqueId val="{00000005-6E7A-6A4E-A238-64DAA2D793D4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:gapWidth val="80"/>
+        <c:overlap val="25"/>
         <c:axId val="516937855"/>
         <c:axId val="516939647"/>
       </c:barChart>
@@ -965,11 +1456,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -981,7 +1472,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1015,8 +1506,8 @@
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1040,7 +1531,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1111,7 +1602,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -1172,6 +1663,931 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
+    <c:name>[LabWeek2.xlsx]PivotDemo!PivotTable1</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent1">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent1">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent1">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent3">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent1">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent4">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.19180314960629918"/>
+          <c:y val="7.407407407407407E-2"/>
+          <c:w val="0.74249781277340332"/>
+          <c:h val="0.84204505686789155"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotDemo!$I$3:$I$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotDemo!$H$5:$H$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotDemo!$I$5:$I$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4933-AB47-A3BC-CBF4117AB002}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotDemo!$J$3:$J$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Feb</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotDemo!$H$5:$H$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotDemo!$J$5:$J$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3350</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-4933-AB47-A3BC-CBF4117AB002}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotDemo!$K$3:$K$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent3">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotDemo!$H$5:$H$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotDemo!$K$5:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2850</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3050</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-4933-AB47-A3BC-CBF4117AB002}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotDemo!$L$3:$L$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent4">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotDemo!$H$5:$H$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotDemo!$L$5:$L$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-4933-AB47-A3BC-CBF4117AB002}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="315"/>
+        <c:overlap val="-40"/>
+        <c:axId val="219462527"/>
+        <c:axId val="219452671"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="219462527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-KG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="219452671"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="219452671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-KG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="219462527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-KG"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-KG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
     <c:name>[LabWeek2.xlsx]Bonus (2)!PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
@@ -1181,11 +2597,527 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="110000"/>
+                  <a:satMod val="105000"/>
+                  <a:tint val="67000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="103000"/>
+                  <a:tint val="73000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="109000"/>
+                  <a:tint val="81000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="110000"/>
+                    <a:satMod val="105000"/>
+                    <a:tint val="67000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="103000"/>
+                    <a:tint val="73000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="109000"/>
+                    <a:tint val="81000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
             <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="110000"/>
+                  <a:satMod val="105000"/>
+                  <a:tint val="67000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="103000"/>
+                  <a:tint val="73000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="109000"/>
+                  <a:tint val="81000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="110000"/>
+                    <a:satMod val="105000"/>
+                    <a:tint val="67000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="103000"/>
+                    <a:tint val="73000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="109000"/>
+                    <a:tint val="81000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="110000"/>
+                  <a:satMod val="105000"/>
+                  <a:tint val="67000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="103000"/>
+                  <a:tint val="73000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="109000"/>
+                  <a:tint val="81000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="110000"/>
+                    <a:satMod val="105000"/>
+                    <a:tint val="67000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="103000"/>
+                    <a:tint val="73000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="109000"/>
+                    <a:tint val="81000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="110000"/>
+                  <a:satMod val="105000"/>
+                  <a:tint val="67000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="103000"/>
+                  <a:tint val="73000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="109000"/>
+                  <a:tint val="81000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="110000"/>
+                    <a:satMod val="105000"/>
+                    <a:tint val="67000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="103000"/>
+                    <a:tint val="73000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="109000"/>
+                    <a:tint val="81000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-KG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="110000"/>
+                  <a:satMod val="105000"/>
+                  <a:tint val="67000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="103000"/>
+                  <a:tint val="73000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="105000"/>
+                  <a:satMod val="109000"/>
+                  <a:tint val="81000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1211,176 +3143,8 @@
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-KG"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-KG"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-KG"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -1424,11 +3188,39 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="110000"/>
+                    <a:satMod val="105000"/>
+                    <a:tint val="67000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="103000"/>
+                    <a:tint val="73000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="109000"/>
+                    <a:tint val="81000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -1486,11 +3278,39 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="110000"/>
+                    <a:satMod val="105000"/>
+                    <a:tint val="67000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="103000"/>
+                    <a:tint val="73000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="109000"/>
+                    <a:tint val="81000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -1529,7 +3349,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D89A-CF45-88D4-5E68E356353A}"/>
+              <c16:uniqueId val="{00000001-04CC-844E-85A9-893EA6B64C02}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1548,11 +3368,39 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="110000"/>
+                    <a:satMod val="105000"/>
+                    <a:tint val="67000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="103000"/>
+                    <a:tint val="73000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="109000"/>
+                    <a:tint val="81000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -1591,7 +3439,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D89A-CF45-88D4-5E68E356353A}"/>
+              <c16:uniqueId val="{00000002-04CC-844E-85A9-893EA6B64C02}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1610,11 +3458,39 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="110000"/>
+                    <a:satMod val="105000"/>
+                    <a:tint val="67000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="103000"/>
+                    <a:tint val="73000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="105000"/>
+                    <a:satMod val="109000"/>
+                    <a:tint val="81000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -1653,7 +3529,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D89A-CF45-88D4-5E68E356353A}"/>
+              <c16:uniqueId val="{00000003-04CC-844E-85A9-893EA6B64C02}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1665,8 +3541,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
         <c:axId val="466712127"/>
         <c:axId val="466703615"/>
       </c:barChart>
@@ -1702,8 +3578,8 @@
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1761,8 +3637,8 @@
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1803,8 +3679,8 @@
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1956,8 +3832,48 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="215">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1968,7 +3884,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1978,6 +3894,1047 @@
       <a:schemeClr val="tx1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="20" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="bg1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="70000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" baseline="0"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="0" i="0" kern="1200" cap="none" spc="50" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
@@ -1998,7 +4955,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -2014,7 +4971,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -2022,8 +4979,8 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2057,36 +5014,62 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="1"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="1"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="15875" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2098,30 +5081,33 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="2">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="1"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="2"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -2138,20 +5124,18 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2166,15 +5150,15 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2185,17 +5169,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2204,17 +5188,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:errorBar>
@@ -2223,21 +5206,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2256,17 +5233,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2275,17 +5251,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2294,17 +5270,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2314,8 +5289,8 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2325,7 +5300,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -2333,7 +5308,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -2342,10 +5317,21 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2353,17 +5339,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -2373,27 +5359,26 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="2"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2403,8 +5388,8 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2423,8 +5408,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2436,8 +5421,8 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2447,517 +5432,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2966,15 +5442,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>321732</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>423333</xdr:colOff>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>59267</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>372532</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>33866</xdr:colOff>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>160867</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3002,16 +5478,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>160866</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>105833</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>296333</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>173566</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>83605</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>465666</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>151338</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -3047,7 +5523,121 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10456333" y="2341033"/>
+              <a:off x="3598333" y="173566"/>
+              <a:ext cx="1828800" cy="2619372"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>808567</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>122767</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>29633</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>21167</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F31EF30-3D8F-8026-AAF7-58574348FC6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>359833</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1172633</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28572</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Month">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFA31853-CF0A-1AC4-6C4C-080EF24C1157}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Month"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10655300" y="254000"/>
               <a:ext cx="1828800" cy="2619372"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3119,6 +5709,240 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>407555</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>581506</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>30881</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Revenue">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E8C4DA4-2777-FA09-49AF-218AF9A31DAB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Revenue"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5372100" y="2260600"/>
+              <a:ext cx="1828800" cy="2619372"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>582276</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>145474</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>756228</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>138255</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="cleanCountry">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F70A8FB-C7F0-419D-3C2D-70BB51D4BA21}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="cleanCountry"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3064549" y="2570019"/>
+              <a:ext cx="1828800" cy="2619372"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>150861</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>195119</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>324812</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>187900</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="cleanProfuct">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80CBA5D2-3361-4C60-D085-11F0D29BA9E8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="cleanProfuct"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="978285" y="3023755"/>
+              <a:ext cx="1828800" cy="2619372"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3145,7 +5969,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Product" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="Laptop"/>
+        <s v="Desktop"/>
+      </sharedItems>
     </cacheField>
     <cacheField name=" Sales" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="800" maxValue="2200"/>
@@ -3166,7 +5993,16 @@
   </cacheSource>
   <cacheFields count="3">
     <cacheField name="Revenue" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="50"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="50" count="8">
+        <n v="14"/>
+        <n v="10"/>
+        <n v="25"/>
+        <n v="15"/>
+        <n v="12"/>
+        <n v="0"/>
+        <n v="6"/>
+        <n v="50"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="cleanCountry" numFmtId="0">
       <sharedItems count="4">
@@ -3187,7 +6023,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="201016731"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -3198,145 +6034,145 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="1500"/>
   </r>
   <r>
     <x v="0"/>
     <x v="0"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1200"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="1700"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1300"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="1600"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1250"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="2100"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1000"/>
   </r>
   <r>
     <x v="1"/>
     <x v="1"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="2200"/>
   </r>
   <r>
     <x v="1"/>
     <x v="1"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1100"/>
   </r>
   <r>
     <x v="1"/>
     <x v="2"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="2000"/>
   </r>
   <r>
     <x v="1"/>
     <x v="2"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1050"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="900"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="800"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="950"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="850"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="1000"/>
   </r>
   <r>
     <x v="2"/>
     <x v="3"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="900"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="1800"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1400"/>
   </r>
   <r>
     <x v="3"/>
     <x v="1"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="1900"/>
   </r>
   <r>
     <x v="3"/>
     <x v="1"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1450"/>
   </r>
   <r>
     <x v="3"/>
     <x v="2"/>
-    <s v="Laptop"/>
+    <x v="0"/>
     <n v="2000"/>
   </r>
   <r>
     <x v="3"/>
     <x v="2"/>
-    <s v="Desktop"/>
+    <x v="1"/>
     <n v="1500"/>
   </r>
 </pivotCacheRecords>
@@ -3345,47 +6181,47 @@
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="9">
   <r>
-    <n v="14"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
   </r>
   <r>
-    <n v="10"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="1"/>
   </r>
   <r>
-    <n v="14"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
   </r>
   <r>
-    <n v="25"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="2"/>
   </r>
   <r>
-    <n v="15"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="1"/>
   </r>
   <r>
-    <n v="12"/>
+    <x v="4"/>
     <x v="3"/>
     <x v="3"/>
   </r>
   <r>
-    <n v="0"/>
+    <x v="5"/>
     <x v="2"/>
     <x v="2"/>
   </r>
   <r>
-    <n v="6"/>
+    <x v="6"/>
     <x v="3"/>
     <x v="3"/>
   </r>
   <r>
-    <n v="50"/>
+    <x v="7"/>
     <x v="2"/>
     <x v="2"/>
   </r>
@@ -3393,7 +6229,79 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DB90D215-7DBA-A144-911F-BB94CD2B1083}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0103867D-ACF3-7247-B859-61FA76F65CB7}" name="PivotTable5" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="N16:S20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of  Sales" fld="3" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DB90D215-7DBA-A144-911F-BB94CD2B1083}" name="PivotTable1" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="H3:M9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -3460,7 +6368,65 @@
   <dataFields count="1">
     <dataField name="Sum of  Sales" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="4">
+  <conditionalFormats count="4">
+    <conditionalFormat priority="5">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="4">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <chartFormats count="8">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
@@ -3509,8 +6475,56 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium23" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -3522,11 +6536,23 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F4C5005-5ED8-CA47-AE76-CEB6F5620F1D}" name="PivotTable4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F4C5005-5ED8-CA47-AE76-CEB6F5620F1D}" name="PivotTable4" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="J2:O8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="9">
+        <item x="5"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="1"/>
@@ -3589,7 +6615,7 @@
   <dataFields count="1">
     <dataField name="Sum of Revenue" fld="0" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="4">
+  <chartFormats count="5">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
@@ -3638,8 +6664,17 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium26" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -3669,9 +6704,95 @@
 </slicerCacheDefinition>
 </file>
 
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Month" xr10:uid="{C21982CF-96A6-4341-A5DB-D800EC0F8CDA}" sourceName="Month">
+  <pivotTables>
+    <pivotTable tabId="2" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="829008328">
+      <items count="4">
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Revenue" xr10:uid="{773DDBC9-B6B4-BB4D-A2BD-69D0D9459F5A}" sourceName="Revenue">
+  <pivotTables>
+    <pivotTable tabId="8" name="PivotTable4"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="201016731">
+      <items count="8">
+        <i x="5" s="1"/>
+        <i x="6" s="1"/>
+        <i x="1" s="1"/>
+        <i x="4" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="7" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_cleanCountry" xr10:uid="{EB97415A-2A55-B540-AAC4-AD7F7CD8014B}" sourceName="cleanCountry">
+  <pivotTables>
+    <pivotTable tabId="8" name="PivotTable4"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="201016731">
+      <items count="4">
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache5.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_cleanProfuct" xr10:uid="{34F5034E-3FEF-A24E-BB0C-3D654F5C3285}" sourceName="cleanProfuct">
+  <pivotTables>
+    <pivotTable tabId="8" name="PivotTable4"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="201016731">
+      <items count="4">
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Region" xr10:uid="{CFE245C0-B6F8-E047-BB59-01ADCA7C2541}" cache="Slicer_Region" caption="Region" rowHeight="251883"/>
+  <slicer name="Month" xr10:uid="{98CC9EA3-CB8C-B24F-A1CF-FB1FD189AFF5}" cache="Slicer_Month" caption="Month" rowHeight="251883"/>
+  <slicer name="Month 1" xr10:uid="{C9BCEAF8-42C1-174E-AF37-CC82FDAD627C}" cache="Slicer_Month" caption="Month" rowHeight="251883"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Revenue" xr10:uid="{8400EFFF-BA2A-C044-829E-F868F9A1155F}" cache="Slicer_Revenue" caption="Revenue" rowHeight="251883"/>
+  <slicer name="cleanCountry" xr10:uid="{E65DEDB3-E800-FC49-92D3-1BAF9B093FD6}" cache="Slicer_cleanCountry" caption="cleanCountry" rowHeight="251883"/>
+  <slicer name="cleanProfuct" xr10:uid="{6E7B9CC3-D8F4-8F4B-80E7-69A4375FE726}" cache="Slicer_cleanProfuct" caption="cleanProfuct" rowHeight="251883"/>
 </slicers>
 </file>
 
@@ -3992,14 +7113,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052E616F-F8E6-E240-867E-43FFFAF8B80B}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="17.83203125" customWidth="1"/>
     <col min="5" max="5" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4015,8 +7136,11 @@
       <c r="E1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4027,15 +7151,19 @@
         <v>1500</v>
       </c>
       <c r="D2" t="str">
-        <f>TRIM(A2)</f>
+        <f t="shared" ref="D2:D10" si="0">TRIM(A2)</f>
         <v>North</v>
       </c>
       <c r="E2" t="str">
-        <f>PROPER(TRIM(B2))</f>
+        <f t="shared" ref="E2:E10" si="1">PROPER(TRIM(B2))</f>
         <v>Laptop</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" t="str">
+        <f>LOWER(E2)</f>
+        <v>laptop</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -4046,15 +7174,19 @@
         <v>1200</v>
       </c>
       <c r="D3" t="str">
-        <f>TRIM(A3)</f>
+        <f t="shared" si="0"/>
         <v>West</v>
       </c>
       <c r="E3" t="str">
-        <f>PROPER(TRIM(B3))</f>
+        <f t="shared" si="1"/>
         <v>Desktop</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F10" si="2">LOWER(E3)</f>
+        <v>desktop</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -4065,15 +7197,19 @@
         <v>0</v>
       </c>
       <c r="D4" t="str">
-        <f>TRIM(A4)</f>
+        <f t="shared" si="0"/>
         <v>East</v>
       </c>
       <c r="E4" t="str">
-        <f>PROPER(TRIM(B4))</f>
+        <f t="shared" si="1"/>
         <v>Tablet</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" t="str">
+        <f t="shared" si="2"/>
+        <v>tablet</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -4084,15 +7220,19 @@
         <v>2100</v>
       </c>
       <c r="D5" t="str">
-        <f>TRIM(A5)</f>
+        <f t="shared" si="0"/>
         <v>South</v>
       </c>
       <c r="E5" t="str">
-        <f>PROPER(TRIM(B5))</f>
+        <f t="shared" si="1"/>
         <v>Laptop</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" t="str">
+        <f t="shared" si="2"/>
+        <v>laptop</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4103,15 +7243,19 @@
         <v>1150</v>
       </c>
       <c r="D6" t="str">
-        <f>TRIM(A6)</f>
+        <f t="shared" si="0"/>
         <v>North</v>
       </c>
       <c r="E6" t="str">
-        <f>PROPER(TRIM(B6))</f>
+        <f t="shared" si="1"/>
         <v>Deckstop</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6" t="str">
+        <f t="shared" si="2"/>
+        <v>deckstop</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -4122,15 +7266,19 @@
         <v>1800</v>
       </c>
       <c r="D7" t="str">
-        <f>TRIM(A7)</f>
+        <f t="shared" si="0"/>
         <v>West</v>
       </c>
       <c r="E7" t="str">
-        <f>PROPER(TRIM(B7))</f>
+        <f t="shared" si="1"/>
         <v>Laptop</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7" t="str">
+        <f t="shared" si="2"/>
+        <v>laptop</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -4141,15 +7289,19 @@
         <v>900</v>
       </c>
       <c r="D8" t="str">
-        <f>TRIM(A8)</f>
+        <f t="shared" si="0"/>
         <v>East</v>
       </c>
       <c r="E8" t="str">
-        <f>PROPER(TRIM(B8))</f>
+        <f t="shared" si="1"/>
         <v>Tablet</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8" t="str">
+        <f t="shared" si="2"/>
+        <v>tablet</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -4160,15 +7312,19 @@
         <v>2000</v>
       </c>
       <c r="D9" t="str">
-        <f>TRIM(A9)</f>
+        <f t="shared" si="0"/>
         <v>South</v>
       </c>
       <c r="E9" t="str">
-        <f>PROPER(TRIM(B9))</f>
+        <f t="shared" si="1"/>
         <v>Desktop</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9" t="str">
+        <f t="shared" si="2"/>
+        <v>desktop</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -4179,12 +7335,26 @@
         <v>950</v>
       </c>
       <c r="D10" t="str">
-        <f>TRIM(A10)</f>
+        <f t="shared" si="0"/>
         <v>East</v>
       </c>
       <c r="E10" t="str">
-        <f>PROPER(TRIM(B10))</f>
+        <f t="shared" si="1"/>
         <v>Tablet</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="2"/>
+        <v>tablet</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D13" s="8">
+        <f>AVERAGE(C2:C10)</f>
+        <v>1288.8888888888889</v>
+      </c>
+      <c r="E13" s="8">
+        <f>AVERAGE(C2:C10)+120%</f>
+        <v>1290.088888888889</v>
       </c>
     </row>
   </sheetData>
@@ -4451,7 +7621,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD75718-56DB-6B41-9D65-463A7010A6C7}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
@@ -4460,9 +7630,18 @@
     <col min="10" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4476,7 +7655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -4490,7 +7669,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -4510,7 +7689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -4542,7 +7721,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -4552,30 +7731,29 @@
       <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5">
         <v>1300</v>
       </c>
-      <c r="E5" s="8"/>
       <c r="H5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>1700</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="7">
         <v>1800</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="7">
         <v>1000</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="7">
         <v>900</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="7">
         <v>5400</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -4591,21 +7769,21 @@
       <c r="H6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>2700</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="7">
         <v>3000</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="7">
         <v>2850</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6">
+      <c r="L6" s="7"/>
+      <c r="M6" s="7">
         <v>8550</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -4621,21 +7799,21 @@
       <c r="H7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <v>3100</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="7">
         <v>3300</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="7">
         <v>3050</v>
       </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6">
+      <c r="L7" s="7"/>
+      <c r="M7" s="7">
         <v>9450</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -4651,21 +7829,21 @@
       <c r="H8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <v>3200</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="7">
         <v>3350</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="7">
         <v>3500</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6">
+      <c r="L8" s="7"/>
+      <c r="M8" s="7">
         <v>10050</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -4681,23 +7859,23 @@
       <c r="H9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <v>10700</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="7">
         <v>11450</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="7">
         <v>10400</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="7">
         <v>900</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="7">
         <v>33450</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -4711,7 +7889,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -4725,7 +7903,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -4739,7 +7917,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -4753,7 +7931,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -4767,7 +7945,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -4781,7 +7959,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
@@ -4794,8 +7972,14 @@
       <c r="D16">
         <v>950</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -4808,8 +7992,26 @@
       <c r="D17">
         <v>850</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O17" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>15</v>
+      </c>
+      <c r="R17" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -4822,8 +8024,26 @@
       <c r="D18">
         <v>1000</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O18" s="7">
+        <v>4</v>
+      </c>
+      <c r="P18" s="7">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>3</v>
+      </c>
+      <c r="R18" s="7">
+        <v>1</v>
+      </c>
+      <c r="S18" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
@@ -4833,8 +8053,24 @@
       <c r="D19">
         <v>900</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O19" s="7">
+        <v>4</v>
+      </c>
+      <c r="P19" s="7">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>4</v>
+      </c>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -4847,8 +8083,26 @@
       <c r="D20">
         <v>1800</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="N20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O20" s="7">
+        <v>8</v>
+      </c>
+      <c r="P20" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>7</v>
+      </c>
+      <c r="R20" s="7">
+        <v>1</v>
+      </c>
+      <c r="S20" s="7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
@@ -4862,7 +8116,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -4876,7 +8130,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
@@ -4890,7 +8144,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
@@ -4904,7 +8158,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>17</v>
       </c>
@@ -4919,15 +8173,29 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="D2:D1048576">
+    <cfRule type="expression" dxfId="2" priority="13" stopIfTrue="1">
       <formula>$D2&gt;1800</formula>
     </cfRule>
-    <cfRule type="top10" dxfId="1" priority="7" rank="10"/>
-    <cfRule type="top10" dxfId="0" priority="8" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="1" priority="19" rank="10"/>
+    <cfRule type="top10" dxfId="0" priority="20" bottom="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5:N8">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6949CFAD-03A4-B144-9103-9051646530A6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="dataBar" priority="5">
+    <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4940,7 +8208,119 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:N8">
+  <conditionalFormatting sqref="H5">
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{369DAC60-5EFB-E840-970D-BA9AD7319AA6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F2DF8123-A478-7849-A15C-5AA2C6C2B5AB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:M4">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9DE9F88D-C42F-CE4E-B7CA-9D3FB5A1FC4D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1E92B18F-120B-6E44-8810-27C14A2B6373}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4E91ABCD-15D3-8E4C-AB5B-7C786DB572E1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="I5:I9">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9EE13311-BE6D-CF46-A16B-E8A9298C9737}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="J5:J9">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{AB3BBDF2-F5F2-4342-9A08-B54016C27C57}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="K5:K9">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{23AA02B8-A8FC-134A-891C-FF919B3C21EB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="L5:L9">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -4949,16 +8329,29 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6949CFAD-03A4-B144-9103-9051646530A6}</x14:id>
+          <x14:id>{18E8745F-7B9C-B548-9EC4-A876C4CE83C9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6949CFAD-03A4-B144-9103-9051646530A6}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N5:N8</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{29F95FC3-6BDF-E24F-A2EB-67CFB896E753}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
@@ -4973,7 +8366,7 @@
           <xm:sqref>M4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6949CFAD-03A4-B144-9103-9051646530A6}">
+          <x14:cfRule type="dataBar" id="{369DAC60-5EFB-E840-970D-BA9AD7319AA6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4983,13 +8376,117 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I5:N8</xm:sqref>
+          <xm:sqref>H5</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F2DF8123-A478-7849-A15C-5AA2C6C2B5AB}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9DE9F88D-C42F-CE4E-B7CA-9D3FB5A1FC4D}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I4:M4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1E92B18F-120B-6E44-8810-27C14A2B6373}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4E91ABCD-15D3-8E4C-AB5B-7C786DB572E1}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I3</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" pivot="1">
+          <x14:cfRule type="dataBar" id="{9EE13311-BE6D-CF46-A16B-E8A9298C9737}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I5:I9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" pivot="1">
+          <x14:cfRule type="dataBar" id="{AB3BBDF2-F5F2-4342-9A08-B54016C27C57}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>J5:J9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" pivot="1">
+          <x14:cfRule type="dataBar" id="{23AA02B8-A8FC-134A-891C-FF919B3C21EB}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K5:K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" pivot="1">
+          <x14:cfRule type="dataBar" id="{18E8745F-7B9C-B548-9EC4-A876C4CE83C9}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L5:L9</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId3"/>
+        <x14:slicer r:id="rId4"/>
       </x14:slicerList>
     </ext>
   </extLst>
@@ -5042,7 +8539,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f>ROW()+999</f>
+        <f t="shared" ref="A2:A10" si="0">ROW()+999</f>
         <v>1001</v>
       </c>
       <c r="B2" t="s">
@@ -5066,7 +8563,7 @@
         <v>Germany</v>
       </c>
       <c r="H2" t="str">
-        <f>CLEAN(TRIM(PROPER(C2)))</f>
+        <f t="shared" ref="H2:H10" si="1">CLEAN(TRIM(PROPER(C2)))</f>
         <v>Mug</v>
       </c>
       <c r="J2" s="4" t="s">
@@ -5078,7 +8575,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B3" t="s">
@@ -5094,15 +8591,15 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F10" si="0">D3*E3</f>
+        <f t="shared" ref="F3:F10" si="2">D3*E3</f>
         <v>10</v>
       </c>
       <c r="G3" t="str">
-        <f>CLEAN(TRIM(PROPER(B3)))</f>
+        <f t="shared" ref="G2:G10" si="3">CLEAN(TRIM(PROPER(B3)))</f>
         <v>France</v>
       </c>
       <c r="H3" t="str">
-        <f>CLEAN(TRIM(PROPER(C3)))</f>
+        <f t="shared" si="1"/>
         <v>Candle</v>
       </c>
       <c r="J3" s="4" t="s">
@@ -5126,7 +8623,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -5142,33 +8639,33 @@
         <v>3.5</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="G4" t="str">
-        <f>CLEAN(TRIM(PROPER(B4)))</f>
+        <f t="shared" si="3"/>
         <v>Germany</v>
       </c>
       <c r="H4" t="str">
-        <f>CLEAN(TRIM(PROPER(C4)))</f>
+        <f t="shared" si="1"/>
         <v>Mug</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="7">
         <v>25</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6">
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B5" t="s">
@@ -5184,33 +8681,33 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="G5" t="str">
-        <f>CLEAN(TRIM(PROPER(B5)))</f>
+        <f t="shared" si="3"/>
         <v>Spain</v>
       </c>
       <c r="H5" t="str">
-        <f>CLEAN(TRIM(PROPER(C5)))</f>
+        <f t="shared" si="1"/>
         <v>Lamp</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6">
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7">
         <v>28</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6">
+      <c r="N5" s="7"/>
+      <c r="O5" s="7">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -5226,33 +8723,33 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="G6" t="str">
-        <f>CLEAN(TRIM(PROPER(B6)))</f>
+        <f t="shared" si="3"/>
         <v>France</v>
       </c>
       <c r="H6" t="str">
-        <f>CLEAN(TRIM(PROPER(C6)))</f>
+        <f t="shared" si="1"/>
         <v>Candle</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6">
+      <c r="K6" s="7"/>
+      <c r="L6" s="7">
         <v>75</v>
       </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6">
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -5268,33 +8765,33 @@
         <v>1.2</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="G7" t="str">
-        <f>CLEAN(TRIM(PROPER(B7)))</f>
+        <f t="shared" si="3"/>
         <v>Uk</v>
       </c>
       <c r="H7" t="str">
-        <f>CLEAN(TRIM(PROPER(C7)))</f>
+        <f t="shared" si="1"/>
         <v>Notebook</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6">
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7">
         <v>18</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="7">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1007</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -5310,39 +8807,39 @@
         <v>25</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <f>CLEAN(TRIM(PROPER(B8)))</f>
+        <f t="shared" si="3"/>
         <v>Spain</v>
       </c>
       <c r="H8" t="str">
-        <f>CLEAN(TRIM(PROPER(C8)))</f>
+        <f t="shared" si="1"/>
         <v>Lamp</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="7">
         <v>25</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="7">
         <v>75</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="7">
         <v>28</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="7">
         <v>18</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="7">
         <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -5358,21 +8855,21 @@
         <v>1.2</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="G9" t="str">
-        <f>CLEAN(TRIM(PROPER(B9)))</f>
+        <f t="shared" si="3"/>
         <v>Uk</v>
       </c>
       <c r="H9" t="str">
-        <f>CLEAN(TRIM(PROPER(C9)))</f>
+        <f t="shared" si="1"/>
         <v>Notebook</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1009</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -5388,15 +8885,15 @@
         <v>25</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="G10" t="str">
-        <f>CLEAN(TRIM(PROPER(B10)))</f>
+        <f t="shared" si="3"/>
         <v>Spain</v>
       </c>
       <c r="H10" t="str">
-        <f>CLEAN(TRIM(PROPER(C10)))</f>
+        <f t="shared" si="1"/>
         <v>Lamp</v>
       </c>
     </row>
@@ -5415,6 +8912,13 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -5448,7 +8952,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f>ROW()+999</f>
+        <f t="shared" ref="A2:A16" si="0">ROW()+999</f>
         <v>1001</v>
       </c>
       <c r="B2" t="s">
@@ -5464,17 +8968,17 @@
         <v>65</v>
       </c>
       <c r="G2" t="str">
-        <f>CLEAN(TRIM(PROPER(B2)))</f>
+        <f t="shared" ref="G2:G16" si="1">CLEAN(TRIM(PROPER(B2)))</f>
         <v>Germany</v>
       </c>
       <c r="H2" t="str">
-        <f>CLEAN(TRIM(PROPER(C2)))</f>
+        <f t="shared" ref="H2:H16" si="2">CLEAN(TRIM(PROPER(C2)))</f>
         <v>Mug</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B3" t="s">
@@ -5490,17 +8994,17 @@
         <v>67</v>
       </c>
       <c r="G3" t="str">
-        <f>CLEAN(TRIM(PROPER(B3)))</f>
+        <f t="shared" si="1"/>
         <v>France</v>
       </c>
       <c r="H3" t="str">
-        <f>CLEAN(TRIM(PROPER(C3)))</f>
+        <f t="shared" si="2"/>
         <v>Candle</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -5516,17 +9020,17 @@
         <v>65</v>
       </c>
       <c r="G4" t="str">
-        <f>CLEAN(TRIM(PROPER(B4)))</f>
+        <f t="shared" si="1"/>
         <v>Germany</v>
       </c>
       <c r="H4" t="str">
-        <f>CLEAN(TRIM(PROPER(C4)))</f>
+        <f t="shared" si="2"/>
         <v>Mug</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B5" t="s">
@@ -5542,17 +9046,17 @@
         <v>68</v>
       </c>
       <c r="G5" t="str">
-        <f>CLEAN(TRIM(PROPER(B5)))</f>
+        <f t="shared" si="1"/>
         <v>Spain</v>
       </c>
       <c r="H5" t="str">
-        <f>CLEAN(TRIM(PROPER(C5)))</f>
+        <f t="shared" si="2"/>
         <v>Lamp</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -5568,17 +9072,17 @@
         <v>67</v>
       </c>
       <c r="G6" t="str">
-        <f>CLEAN(TRIM(PROPER(B6)))</f>
+        <f t="shared" si="1"/>
         <v>France</v>
       </c>
       <c r="H6" t="str">
-        <f>CLEAN(TRIM(PROPER(C6)))</f>
+        <f t="shared" si="2"/>
         <v>Candle</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -5594,17 +9098,17 @@
         <v>66</v>
       </c>
       <c r="G7" t="str">
-        <f>CLEAN(TRIM(PROPER(B7)))</f>
+        <f t="shared" si="1"/>
         <v>Uk</v>
       </c>
       <c r="H7" t="str">
-        <f>CLEAN(TRIM(PROPER(C7)))</f>
+        <f t="shared" si="2"/>
         <v>Notebook</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1007</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -5620,17 +9124,17 @@
         <v>65</v>
       </c>
       <c r="G8" t="str">
-        <f>CLEAN(TRIM(PROPER(B8)))</f>
+        <f t="shared" si="1"/>
         <v>Germany</v>
       </c>
       <c r="H8" t="str">
-        <f>CLEAN(TRIM(PROPER(C8)))</f>
+        <f t="shared" si="2"/>
         <v>Mug</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -5646,17 +9150,17 @@
         <v>68</v>
       </c>
       <c r="G9" t="str">
-        <f>CLEAN(TRIM(PROPER(B9)))</f>
+        <f t="shared" si="1"/>
         <v>Spain</v>
       </c>
       <c r="H9" t="str">
-        <f>CLEAN(TRIM(PROPER(C9)))</f>
+        <f t="shared" si="2"/>
         <v>Lamp</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1009</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -5672,17 +9176,17 @@
         <v>66</v>
       </c>
       <c r="G10" t="str">
-        <f>CLEAN(TRIM(PROPER(B10)))</f>
+        <f t="shared" si="1"/>
         <v>Uk</v>
       </c>
       <c r="H10" t="str">
-        <f>CLEAN(TRIM(PROPER(C10)))</f>
+        <f t="shared" si="2"/>
         <v>Notebook</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1010</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -5698,17 +9202,17 @@
         <v>67</v>
       </c>
       <c r="G11" t="str">
-        <f>CLEAN(TRIM(PROPER(B11)))</f>
+        <f t="shared" si="1"/>
         <v>France</v>
       </c>
       <c r="H11" t="str">
-        <f>CLEAN(TRIM(PROPER(C11)))</f>
+        <f t="shared" si="2"/>
         <v>Candle</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1011</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -5724,17 +9228,17 @@
         <v>65</v>
       </c>
       <c r="G12" t="str">
-        <f>CLEAN(TRIM(PROPER(B12)))</f>
+        <f t="shared" si="1"/>
         <v>Germany</v>
       </c>
       <c r="H12" t="str">
-        <f>CLEAN(TRIM(PROPER(C12)))</f>
+        <f t="shared" si="2"/>
         <v>Mug</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1012</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -5750,17 +9254,17 @@
         <v>66</v>
       </c>
       <c r="G13" t="str">
-        <f>CLEAN(TRIM(PROPER(B13)))</f>
+        <f t="shared" si="1"/>
         <v>Uk</v>
       </c>
       <c r="H13" t="str">
-        <f>CLEAN(TRIM(PROPER(C13)))</f>
+        <f t="shared" si="2"/>
         <v>Notebook</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1013</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -5776,17 +9280,17 @@
         <v>68</v>
       </c>
       <c r="G14" t="str">
-        <f>CLEAN(TRIM(PROPER(B14)))</f>
+        <f t="shared" si="1"/>
         <v>Spain</v>
       </c>
       <c r="H14" t="str">
-        <f>CLEAN(TRIM(PROPER(C14)))</f>
+        <f t="shared" si="2"/>
         <v>Lamp</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1014</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -5802,17 +9306,17 @@
         <v>67</v>
       </c>
       <c r="G15" t="str">
-        <f>CLEAN(TRIM(PROPER(B15)))</f>
+        <f t="shared" si="1"/>
         <v>France</v>
       </c>
       <c r="H15" t="str">
-        <f>CLEAN(TRIM(PROPER(C15)))</f>
+        <f t="shared" si="2"/>
         <v>Candle</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f>ROW()+999</f>
+        <f t="shared" si="0"/>
         <v>1015</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -5828,11 +9332,11 @@
         <v>65</v>
       </c>
       <c r="G16" t="str">
-        <f>CLEAN(TRIM(PROPER(B16)))</f>
+        <f t="shared" si="1"/>
         <v>Germany</v>
       </c>
       <c r="H16" t="str">
-        <f>CLEAN(TRIM(PROPER(C16)))</f>
+        <f t="shared" si="2"/>
         <v>Mug</v>
       </c>
     </row>
@@ -5894,7 +9398,7 @@
       <c r="B5">
         <v>11500</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>0.17</v>
       </c>
     </row>
@@ -5905,7 +9409,7 @@
       <c r="B6">
         <v>11700</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>0.02</v>
       </c>
     </row>
@@ -5916,7 +9420,7 @@
       <c r="B7">
         <v>9000</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>-0.23</v>
       </c>
     </row>
@@ -5960,10 +9464,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A75641-A7CD-6242-B897-A219155FC09E}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -5974,7 +9478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5984,8 +9488,12 @@
       <c r="C2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" t="e">
+        <f>VLOOKUP(B$2,Products!A$2,Orders!B$2,FALSE)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5996,7 +9504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6007,7 +9515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6018,7 +9526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6029,7 +9537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6040,7 +9548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6051,7 +9559,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6069,7 +9577,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D22D2EE-AD19-774C-94C2-500A24C5FD6E}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -6086,6 +9594,118 @@
         <v>27</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9">
+        <v>2000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
